--- a/mom/docs/forms/frm-200-purchase/FRM-209_High_Risk_Job_Readiness_Review.xlsx
+++ b/mom/docs/forms/frm-200-purchase/FRM-209_High_Risk_Job_Readiness_Review.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="FRM_209" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="LISTS" sheetId="2" state="hidden" r:id="rId2"/>
+    <sheet name="FRM_209" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="LISTS" sheetId="2" state="hidden" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="191029" fullCalcOnLoad="1"/>
@@ -827,7 +827,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="252">
+  <borders count="253">
     <border>
       <left/>
       <right/>
@@ -3651,12 +3651,16 @@
         <color rgb="000078D4"/>
       </bottom>
       <diagonal/>
+    </border>
+    <border>
+      <right/>
+      <bottom/>
     </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1"/>
   </cellStyleXfs>
-  <cellXfs count="519">
+  <cellXfs count="520">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
@@ -4904,6 +4908,7 @@
     <xf numFmtId="0" fontId="89" fillId="48" borderId="213" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="47" borderId="252" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -5105,36 +5110,6 @@
     </comment>
   </commentList>
 </comments>
-</file>
-
-<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
-  <oneCellAnchor>
-    <from>
-      <col>0</col>
-      <colOff>161925</colOff>
-      <row>1</row>
-      <rowOff>314325</rowOff>
-    </from>
-    <ext cx="1123950" cy="323850"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="1" name="Image 1" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId1"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-</wsDr>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -5539,7 +5514,7 @@
       <c r="AH3" s="15" t="n"/>
       <c r="AI3" s="293" t="inlineStr">
         <is>
-          <t>Rev.01</t>
+          <t>Rev.02</t>
         </is>
       </c>
       <c r="AJ3" s="14" t="n"/>
@@ -5582,7 +5557,7 @@
       <c r="AH4" s="15" t="n"/>
       <c r="AI4" s="293" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-05-21</t>
         </is>
       </c>
       <c r="AJ4" s="14" t="n"/>
@@ -5672,7 +5647,7 @@
       <c r="AN6" s="272" t="n"/>
     </row>
     <row r="7" ht="4" customHeight="1" s="264">
-      <c r="A7" s="469" t="n"/>
+      <c r="A7" s="519" t="n"/>
       <c r="B7" s="26" t="n"/>
       <c r="C7" s="26" t="n"/>
       <c r="D7" s="26" t="n"/>
@@ -5860,7 +5835,7 @@
       <c r="AN10" s="486" t="n"/>
     </row>
     <row r="11" ht="4" customHeight="1" s="264">
-      <c r="A11" s="469" t="n"/>
+      <c r="A11" s="519" t="n"/>
       <c r="B11" s="26" t="n"/>
       <c r="C11" s="26" t="n"/>
       <c r="D11" s="26" t="n"/>
@@ -6475,10 +6450,18 @@
         <v/>
       </c>
       <c r="B22" s="491" t="n"/>
-      <c r="C22" s="504" t="n"/>
+      <c r="C22" s="503" t="inlineStr">
+        <is>
+          <t>CAP</t>
+        </is>
+      </c>
       <c r="D22" s="493" t="n"/>
       <c r="E22" s="491" t="n"/>
-      <c r="F22" s="505" t="n"/>
+      <c r="F22" s="500" t="inlineStr">
+        <is>
+          <t>Shop-floor manufacturability reviewed with CNC Workshop Manager (WKM).</t>
+        </is>
+      </c>
       <c r="G22" s="493" t="n"/>
       <c r="H22" s="493" t="n"/>
       <c r="I22" s="493" t="n"/>
@@ -6494,7 +6477,11 @@
       <c r="S22" s="493" t="n"/>
       <c r="T22" s="493" t="n"/>
       <c r="U22" s="491" t="n"/>
-      <c r="V22" s="504" t="n"/>
+      <c r="V22" s="495" t="inlineStr">
+        <is>
+          <t>WKM confirms machine condition, fixture availability and operator skill match → PASS.</t>
+        </is>
+      </c>
       <c r="W22" s="493" t="n"/>
       <c r="X22" s="493" t="n"/>
       <c r="Y22" s="493" t="n"/>
@@ -6560,7 +6547,7 @@
       <c r="AN23" s="486" t="n"/>
     </row>
     <row r="24" ht="4" customHeight="1" s="264">
-      <c r="A24" s="469" t="n"/>
+      <c r="A24" s="519" t="n"/>
       <c r="B24" s="26" t="n"/>
       <c r="C24" s="26" t="n"/>
       <c r="D24" s="26" t="n"/>
@@ -6796,7 +6783,7 @@
       <c r="AN29" s="486" t="n"/>
     </row>
     <row r="30" ht="4" customHeight="1" s="264">
-      <c r="A30" s="469" t="n"/>
+      <c r="A30" s="519" t="n"/>
       <c r="B30" s="26" t="n"/>
       <c r="C30" s="26" t="n"/>
       <c r="D30" s="26" t="n"/>
@@ -7004,7 +6991,6 @@
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait" paperSize="9" fitToHeight="0" fitToWidth="1"/>
-  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
   <legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="anysvml"/>
 </worksheet>
 </file>
